--- a/scripts/teacher-imports/account-provisioning/inputs/teacher-accounts-import-5.xlsx
+++ b/scripts/teacher-imports/account-provisioning/inputs/teacher-accounts-import-5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\edu-affairs-v2\scripts\teacher-imports\account-provisioning\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{272B9F45-10F9-4108-88FB-3D0F5EFF6C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C829D8-0A59-427D-95F4-0344BD85EAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1275" yWindow="2370" windowWidth="15645" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="210" yWindow="2760" windowWidth="11820" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="المعلمين" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
   <si>
     <t>الاسم الكامل</t>
   </si>
@@ -118,16 +118,25 @@
     <t>BOYS_TEACHER لمعلمي البنين، أو GIRLS_TEACHER لمعلمات البنات.  -- KG_TEACHER</t>
   </si>
   <si>
-    <t>حامد السيد السيد نافع</t>
-  </si>
-  <si>
-    <t>hameed-s@qz.org.sa</t>
-  </si>
-  <si>
-    <t>KF100000030</t>
-  </si>
-  <si>
-    <t>BOYS_TEACHER</t>
+    <t>KG_TEACHER</t>
+  </si>
+  <si>
+    <t>m.a.almansor@qz.org.sa</t>
+  </si>
+  <si>
+    <t>KF100000122</t>
+  </si>
+  <si>
+    <t>ميعاد احمد عبداللطيف المنصور</t>
+  </si>
+  <si>
+    <t>منار جبر احمد الجبر</t>
+  </si>
+  <si>
+    <t>KF100000100</t>
+  </si>
+  <si>
+    <t>m.aljabr@qz.org.sa</t>
   </si>
 </sst>
 </file>
@@ -287,7 +296,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeacherAccountsImportTable" displayName="TeacherAccountsImportTable" ref="A1:H2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TeacherAccountsImportTable" displayName="TeacherAccountsImportTable" ref="A1:H3">
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="الاسم الكامل"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="البريد الإلكتروني"/>
@@ -451,11 +460,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="24.5" customWidth="1"/>
-    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.25" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.25" bestFit="1" customWidth="1"/>
@@ -492,31 +501,54 @@
     </row>
     <row r="2" spans="1:8" ht="16.5">
       <c r="A2" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>29</v>
       </c>
       <c r="C2" s="7">
-        <v>2550897843</v>
+        <v>1108035914</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>30</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="16.5">
+      <c r="A3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="7">
+        <v>1092912201</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="G2" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="G2:G3" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"نشط,غير نشط"</formula1>
     </dataValidation>
   </dataValidations>
